--- a/sample_imports/06_GiangVien_Mau.xlsx
+++ b/sample_imports/06_GiangVien_Mau.xlsx
@@ -7,7 +7,7 @@
     <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="DuLieuMau" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
@@ -15,10 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="28">
-  <si>
-    <t>MẪU DỮ LIỆU GIẢNG VIÊN</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="289">
   <si>
     <t>MaGV</t>
   </si>
@@ -50,55 +47,841 @@
     <t>TrangThai</t>
   </si>
   <si>
-    <t>GV91</t>
-  </si>
-  <si>
-    <t>Vũ Thị Thanh Mai</t>
-  </si>
-  <si>
-    <t>gv91_test@huit.edu.vn</t>
-  </si>
-  <si>
-    <t>0981112233</t>
-  </si>
-  <si>
-    <t>1982-04-12</t>
+    <t>GV001</t>
+  </si>
+  <si>
+    <t>PGS.TS. Nguyễn Văn Hùng</t>
+  </si>
+  <si>
+    <t>hungnv@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123001</t>
+  </si>
+  <si>
+    <t>1975-04-12</t>
+  </si>
+  <si>
+    <t>Nam</t>
+  </si>
+  <si>
+    <t>Phó Giáo sư</t>
+  </si>
+  <si>
+    <t>Tiến sĩ</t>
+  </si>
+  <si>
+    <t>KHMT</t>
+  </si>
+  <si>
+    <t>Đang công tác</t>
+  </si>
+  <si>
+    <t>GV002</t>
+  </si>
+  <si>
+    <t>TS. Trần Anh Dũng</t>
+  </si>
+  <si>
+    <t>dungta@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123002</t>
+  </si>
+  <si>
+    <t>1979-08-20</t>
+  </si>
+  <si>
+    <t>CNPM</t>
+  </si>
+  <si>
+    <t>GV003</t>
+  </si>
+  <si>
+    <t>TS. Phạm Minh Tuấn</t>
+  </si>
+  <si>
+    <t>tuanpm@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123003</t>
+  </si>
+  <si>
+    <t>1982-11-15</t>
+  </si>
+  <si>
+    <t>HTTT</t>
+  </si>
+  <si>
+    <t>GV004</t>
+  </si>
+  <si>
+    <t>TS. Trịnh Văn Thành</t>
+  </si>
+  <si>
+    <t>thanhtv@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123004</t>
+  </si>
+  <si>
+    <t>1980-02-18</t>
+  </si>
+  <si>
+    <t>ATTT</t>
+  </si>
+  <si>
+    <t>GV005</t>
+  </si>
+  <si>
+    <t>TS. Lê Hải Đăng</t>
+  </si>
+  <si>
+    <t>danglh@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123005</t>
+  </si>
+  <si>
+    <t>1984-06-25</t>
+  </si>
+  <si>
+    <t>MMT</t>
+  </si>
+  <si>
+    <t>GV006</t>
+  </si>
+  <si>
+    <t>PGS.TS. Võ Quốc Phong</t>
+  </si>
+  <si>
+    <t>phongvq@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123006</t>
+  </si>
+  <si>
+    <t>1976-09-30</t>
+  </si>
+  <si>
+    <t>GV007</t>
+  </si>
+  <si>
+    <t>TS. Đỗ Anh Minh</t>
+  </si>
+  <si>
+    <t>minhda@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123007</t>
+  </si>
+  <si>
+    <t>1985-03-14</t>
+  </si>
+  <si>
+    <t>KHDL</t>
+  </si>
+  <si>
+    <t>GV008</t>
+  </si>
+  <si>
+    <t>PGS.TS. Trần Đình Nam</t>
+  </si>
+  <si>
+    <t>namtd@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123008</t>
+  </si>
+  <si>
+    <t>1974-12-05</t>
+  </si>
+  <si>
+    <t>QTKD_DN</t>
+  </si>
+  <si>
+    <t>GV009</t>
+  </si>
+  <si>
+    <t>GS.TS. Lê Thị Mai</t>
+  </si>
+  <si>
+    <t>mailt@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123009</t>
+  </si>
+  <si>
+    <t>1970-07-22</t>
   </si>
   <si>
     <t>Nữ</t>
   </si>
   <si>
-    <t>Tiến sĩ</t>
-  </si>
-  <si>
-    <t>BMANH</t>
-  </si>
-  <si>
-    <t>Đang công tác</t>
-  </si>
-  <si>
-    <t>GV92</t>
-  </si>
-  <si>
-    <t>Đỗ Quốc Bảo</t>
-  </si>
-  <si>
-    <t>gv92_test@huit.edu.vn</t>
-  </si>
-  <si>
-    <t>0982223344</t>
-  </si>
-  <si>
-    <t>1979-09-25</t>
-  </si>
-  <si>
-    <t>Nam</t>
-  </si>
-  <si>
-    <t>Phó Giáo sư</t>
-  </si>
-  <si>
-    <t>BMQTKD</t>
+    <t>Giáo sư</t>
+  </si>
+  <si>
+    <t>CBTP</t>
+  </si>
+  <si>
+    <t>GV010</t>
+  </si>
+  <si>
+    <t>PGS.TS. Vũ Trọng Hưng</t>
+  </si>
+  <si>
+    <t>hungvt@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123010</t>
+  </si>
+  <si>
+    <t>1973-05-19</t>
+  </si>
+  <si>
+    <t>KTD</t>
+  </si>
+  <si>
+    <t>GV011</t>
+  </si>
+  <si>
+    <t>TS. Bùi Thu Hà</t>
+  </si>
+  <si>
+    <t>habth@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123011</t>
+  </si>
+  <si>
+    <t>1983-10-10</t>
+  </si>
+  <si>
+    <t>GV012</t>
+  </si>
+  <si>
+    <t>TS. Nguyễn Văn An</t>
+  </si>
+  <si>
+    <t>annv@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123012</t>
+  </si>
+  <si>
+    <t>1981-01-28</t>
+  </si>
+  <si>
+    <t>MKT</t>
+  </si>
+  <si>
+    <t>GV013</t>
+  </si>
+  <si>
+    <t>PGS.TS. Đỗ Hoài Nam</t>
+  </si>
+  <si>
+    <t>namdh@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123013</t>
+  </si>
+  <si>
+    <t>1977-03-08</t>
+  </si>
+  <si>
+    <t>GV014</t>
+  </si>
+  <si>
+    <t>TS. Trương Tuyết Mai</t>
+  </si>
+  <si>
+    <t>maitt@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123014</t>
+  </si>
+  <si>
+    <t>1986-09-17</t>
+  </si>
+  <si>
+    <t>DBTP</t>
+  </si>
+  <si>
+    <t>GV015</t>
+  </si>
+  <si>
+    <t>TS. Vũ Anh Quân</t>
+  </si>
+  <si>
+    <t>quanva@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123015</t>
+  </si>
+  <si>
+    <t>1982-04-03</t>
+  </si>
+  <si>
+    <t>GV016</t>
+  </si>
+  <si>
+    <t>TS. Hồ Vĩnh Thắng</t>
+  </si>
+  <si>
+    <t>thanghv@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123016</t>
+  </si>
+  <si>
+    <t>1980-11-29</t>
+  </si>
+  <si>
+    <t>DT</t>
+  </si>
+  <si>
+    <t>GV017</t>
+  </si>
+  <si>
+    <t>PGS.TS. Đặng Quốc Thịnh</t>
+  </si>
+  <si>
+    <t>thinhdq@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123017</t>
+  </si>
+  <si>
+    <t>1972-08-16</t>
+  </si>
+  <si>
+    <t>CTM</t>
+  </si>
+  <si>
+    <t>GV018</t>
+  </si>
+  <si>
+    <t>TS. Phan Trọng Nghĩa</t>
+  </si>
+  <si>
+    <t>nghiapt@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123018</t>
+  </si>
+  <si>
+    <t>1983-02-11</t>
+  </si>
+  <si>
+    <t>GV019</t>
+  </si>
+  <si>
+    <t>TS. Chu Văn Quân</t>
+  </si>
+  <si>
+    <t>quancv@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123019</t>
+  </si>
+  <si>
+    <t>1981-12-24</t>
+  </si>
+  <si>
+    <t>CDT</t>
+  </si>
+  <si>
+    <t>GV020</t>
+  </si>
+  <si>
+    <t>TS. Phạm Thị Bích Loan</t>
+  </si>
+  <si>
+    <t>loanptb@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123020</t>
+  </si>
+  <si>
+    <t>1978-06-30</t>
+  </si>
+  <si>
+    <t>TA_CN</t>
+  </si>
+  <si>
+    <t>GV021</t>
+  </si>
+  <si>
+    <t>ThS. Đặng Hải Giang</t>
+  </si>
+  <si>
+    <t>giangdh@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123021</t>
+  </si>
+  <si>
+    <t>1988-05-14</t>
+  </si>
+  <si>
+    <t>Thạc sĩ</t>
+  </si>
+  <si>
+    <t>GV022</t>
+  </si>
+  <si>
+    <t>ThS. Trần Thị Bích</t>
+  </si>
+  <si>
+    <t>bichtb@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123022</t>
+  </si>
+  <si>
+    <t>1989-09-02</t>
+  </si>
+  <si>
+    <t>GV023</t>
+  </si>
+  <si>
+    <t>TS. Lê Hoàng Cường</t>
+  </si>
+  <si>
+    <t>cuonglh@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123023</t>
+  </si>
+  <si>
+    <t>1984-12-18</t>
+  </si>
+  <si>
+    <t>GV024</t>
+  </si>
+  <si>
+    <t>ThS. Ngô Đức Hải</t>
+  </si>
+  <si>
+    <t>haind@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123024</t>
+  </si>
+  <si>
+    <t>1990-07-07</t>
+  </si>
+  <si>
+    <t>GV025</t>
+  </si>
+  <si>
+    <t>TS. Dương Thúy Hằng</t>
+  </si>
+  <si>
+    <t>hangdt@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123025</t>
+  </si>
+  <si>
+    <t>1983-04-26</t>
+  </si>
+  <si>
+    <t>GV026</t>
+  </si>
+  <si>
+    <t>ThS. Lý Thanh Lan</t>
+  </si>
+  <si>
+    <t>lanlt@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123026</t>
+  </si>
+  <si>
+    <t>1991-02-14</t>
+  </si>
+  <si>
+    <t>GV027</t>
+  </si>
+  <si>
+    <t>TS. Trịnh Văn Khang</t>
+  </si>
+  <si>
+    <t>khangtv@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123027</t>
+  </si>
+  <si>
+    <t>1982-08-09</t>
+  </si>
+  <si>
+    <t>GV028</t>
+  </si>
+  <si>
+    <t>ThS. Mai Tuyết Nga</t>
+  </si>
+  <si>
+    <t>ngamt@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123028</t>
+  </si>
+  <si>
+    <t>1987-11-21</t>
+  </si>
+  <si>
+    <t>GV029</t>
+  </si>
+  <si>
+    <t>TS. Võ Đình Phúc</t>
+  </si>
+  <si>
+    <t>phucvd@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123029</t>
+  </si>
+  <si>
+    <t>1980-03-31</t>
+  </si>
+  <si>
+    <t>GV030</t>
+  </si>
+  <si>
+    <t>ThS. Hoàng Thị Em</t>
+  </si>
+  <si>
+    <t>emht@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123030</t>
+  </si>
+  <si>
+    <t>1992-01-19</t>
+  </si>
+  <si>
+    <t>GV031</t>
+  </si>
+  <si>
+    <t>TS. Đinh Hoàng Xuân</t>
+  </si>
+  <si>
+    <t>xuandh@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123031</t>
+  </si>
+  <si>
+    <t>1985-06-12</t>
+  </si>
+  <si>
+    <t>KT</t>
+  </si>
+  <si>
+    <t>GV032</t>
+  </si>
+  <si>
+    <t>TS. Cao Thái Vinh</t>
+  </si>
+  <si>
+    <t>vinhct@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123032</t>
+  </si>
+  <si>
+    <t>1984-10-05</t>
+  </si>
+  <si>
+    <t>TC</t>
+  </si>
+  <si>
+    <t>GV033</t>
+  </si>
+  <si>
+    <t>TS. Phan Văn Phúc</t>
+  </si>
+  <si>
+    <t>phucpv@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123033</t>
+  </si>
+  <si>
+    <t>1979-05-23</t>
+  </si>
+  <si>
+    <t>LKTE</t>
+  </si>
+  <si>
+    <t>GV034</t>
+  </si>
+  <si>
+    <t>TS. Hoàng Yến Linh</t>
+  </si>
+  <si>
+    <t>linhhy@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123034</t>
+  </si>
+  <si>
+    <t>1986-07-15</t>
+  </si>
+  <si>
+    <t>QTDL</t>
+  </si>
+  <si>
+    <t>GV035</t>
+  </si>
+  <si>
+    <t>TS. Bùi Mai Hoa</t>
+  </si>
+  <si>
+    <t>hoabm@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123035</t>
+  </si>
+  <si>
+    <t>1981-09-09</t>
+  </si>
+  <si>
+    <t>KHMT_MT</t>
+  </si>
+  <si>
+    <t>GV036</t>
+  </si>
+  <si>
+    <t>TS. Võ Duy Hùng</t>
+  </si>
+  <si>
+    <t>hungvd@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123036</t>
+  </si>
+  <si>
+    <t>1983-02-27</t>
+  </si>
+  <si>
+    <t>TMDT_SO</t>
+  </si>
+  <si>
+    <t>GV037</t>
+  </si>
+  <si>
+    <t>PGS.TS. Mai Thế Vinh</t>
+  </si>
+  <si>
+    <t>vinhtm@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123037</t>
+  </si>
+  <si>
+    <t>1975-11-11</t>
+  </si>
+  <si>
+    <t>LOG_CCU</t>
+  </si>
+  <si>
+    <t>GV038</t>
+  </si>
+  <si>
+    <t>ThS. Nguyễn Hoàng Anh</t>
+  </si>
+  <si>
+    <t>anhnh@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123038</t>
+  </si>
+  <si>
+    <t>1989-08-18</t>
+  </si>
+  <si>
+    <t>GV039</t>
+  </si>
+  <si>
+    <t>ThS. Lê Phương Thảo</t>
+  </si>
+  <si>
+    <t>thaolp@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123039</t>
+  </si>
+  <si>
+    <t>1990-12-03</t>
+  </si>
+  <si>
+    <t>GV040</t>
+  </si>
+  <si>
+    <t>TS. Vũ Đình Khôi</t>
+  </si>
+  <si>
+    <t>khoivd@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123040</t>
+  </si>
+  <si>
+    <t>1984-04-17</t>
+  </si>
+  <si>
+    <t>GV041</t>
+  </si>
+  <si>
+    <t>ThS. Huỳnh Quốc Bảo</t>
+  </si>
+  <si>
+    <t>baohq@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123041</t>
+  </si>
+  <si>
+    <t>1991-03-25</t>
+  </si>
+  <si>
+    <t>GV042</t>
+  </si>
+  <si>
+    <t>TS. Tôn Nữ Quỳnh Như</t>
+  </si>
+  <si>
+    <t>nhutnq@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123042</t>
+  </si>
+  <si>
+    <t>1987-10-30</t>
+  </si>
+  <si>
+    <t>GV043</t>
+  </si>
+  <si>
+    <t>ThS. Cù Huy Sơn</t>
+  </si>
+  <si>
+    <t>sonch@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123043</t>
+  </si>
+  <si>
+    <t>1988-06-19</t>
+  </si>
+  <si>
+    <t>GV044</t>
+  </si>
+  <si>
+    <t>TS. Thạch Văn Tài</t>
+  </si>
+  <si>
+    <t>taitv@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123044</t>
+  </si>
+  <si>
+    <t>1983-01-08</t>
+  </si>
+  <si>
+    <t>GV045</t>
+  </si>
+  <si>
+    <t>ThS. Uông Thị Uyên</t>
+  </si>
+  <si>
+    <t>uyenut@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123045</t>
+  </si>
+  <si>
+    <t>1992-09-14</t>
+  </si>
+  <si>
+    <t>GV046</t>
+  </si>
+  <si>
+    <t>TS. Phí Văn Việt</t>
+  </si>
+  <si>
+    <t>vietpv@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123046</t>
+  </si>
+  <si>
+    <t>1985-05-22</t>
+  </si>
+  <si>
+    <t>GV047</t>
+  </si>
+  <si>
+    <t>ThS. Mạc Thị Xuyến</t>
+  </si>
+  <si>
+    <t>xuyenmt@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123047</t>
+  </si>
+  <si>
+    <t>1990-08-04</t>
+  </si>
+  <si>
+    <t>GV048</t>
+  </si>
+  <si>
+    <t>TS. La Quốc Ý</t>
+  </si>
+  <si>
+    <t>ylq@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123048</t>
+  </si>
+  <si>
+    <t>1982-12-16</t>
+  </si>
+  <si>
+    <t>GV049</t>
+  </si>
+  <si>
+    <t>ThS. Sầm Ngọc Anh</t>
+  </si>
+  <si>
+    <t>anhsn@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123049</t>
+  </si>
+  <si>
+    <t>1993-04-11</t>
+  </si>
+  <si>
+    <t>GV050</t>
+  </si>
+  <si>
+    <t>TS. Nông Văn Bắc</t>
+  </si>
+  <si>
+    <t>bacnv@huit.edu.vn</t>
+  </si>
+  <si>
+    <t>0903123050</t>
+  </si>
+  <si>
+    <t>1981-07-29</t>
   </si>
 </sst>
 </file>
@@ -106,7 +889,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <b val="0"/>
       <i val="0"/>
@@ -116,52 +899,16 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="13"/>
-      <color rgb="FF1E3A8A"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E40AF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FAFC"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -169,54 +916,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF93C5FD"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF93C5FD"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF93C5FD"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF93C5FD"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFE2E8F0"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFE2E8F0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFE2E8F0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFE2E8F0"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="1">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="2" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="4" borderId="2" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -516,124 +1221,1570 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="19.995" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="25.851" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="16.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="6.998" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="28.136" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="23.423" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="13.997" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="10.569" bestFit="true" customWidth="true" style="0"/>
     <col min="7" max="7" width="13.997" bestFit="true" customWidth="true" style="0"/>
     <col min="8" max="8" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="11.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="9" max="9" width="9.283" bestFit="true" customWidth="true" style="0"/>
     <col min="10" max="10" width="16.425" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" customHeight="1" ht="28">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" customHeight="1" ht="24">
-      <c r="A2" s="2" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="2" t="s">
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" customHeight="1" ht="20">
-      <c r="A3" s="3" t="s">
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D2" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E2" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="3" t="s">
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" customHeight="1" ht="20">
-      <c r="A4" s="4" t="s">
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B3" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C3" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D3" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E3" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3"/>
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="J3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="4" t="s">
+      <c r="B4" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4"/>
+      <c r="H4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5"/>
+      <c r="H5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6"/>
+      <c r="H6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8"/>
+      <c r="H8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" t="s">
+        <v>54</v>
+      </c>
+      <c r="J8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" t="s">
+        <v>60</v>
+      </c>
+      <c r="J9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" t="s">
+        <v>68</v>
+      </c>
+      <c r="J10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" t="s">
+        <v>73</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" t="s">
+        <v>74</v>
+      </c>
+      <c r="J11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D12" t="s">
+        <v>78</v>
+      </c>
+      <c r="E12" t="s">
+        <v>79</v>
+      </c>
+      <c r="F12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12"/>
+      <c r="H12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" t="s">
+        <v>60</v>
+      </c>
+      <c r="J12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" t="s">
+        <v>84</v>
+      </c>
+      <c r="F13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13"/>
+      <c r="H13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" t="s">
+        <v>85</v>
+      </c>
+      <c r="J13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" t="s">
+        <v>89</v>
+      </c>
+      <c r="E14" t="s">
+        <v>90</v>
+      </c>
+      <c r="F14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" t="s">
+        <v>68</v>
+      </c>
+      <c r="J14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D15" t="s">
+        <v>94</v>
+      </c>
+      <c r="E15" t="s">
+        <v>95</v>
+      </c>
+      <c r="F15" t="s">
+        <v>66</v>
+      </c>
+      <c r="G15"/>
+      <c r="H15" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" t="s">
+        <v>96</v>
+      </c>
+      <c r="J15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" t="s">
+        <v>99</v>
+      </c>
+      <c r="D16" t="s">
+        <v>100</v>
+      </c>
+      <c r="E16" t="s">
+        <v>101</v>
+      </c>
+      <c r="F16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16"/>
+      <c r="H16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" t="s">
+        <v>74</v>
+      </c>
+      <c r="J16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" t="s">
+        <v>103</v>
+      </c>
+      <c r="C17" t="s">
+        <v>104</v>
+      </c>
+      <c r="D17" t="s">
+        <v>105</v>
+      </c>
+      <c r="E17" t="s">
+        <v>106</v>
+      </c>
+      <c r="F17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17"/>
+      <c r="H17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I17" t="s">
+        <v>107</v>
+      </c>
+      <c r="J17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" t="s">
+        <v>108</v>
+      </c>
+      <c r="B18" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18" t="s">
+        <v>110</v>
+      </c>
+      <c r="D18" t="s">
+        <v>111</v>
+      </c>
+      <c r="E18" t="s">
+        <v>112</v>
+      </c>
+      <c r="F18" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" t="s">
+        <v>17</v>
+      </c>
+      <c r="I18" t="s">
+        <v>113</v>
+      </c>
+      <c r="J18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" t="s">
+        <v>114</v>
+      </c>
+      <c r="B19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C19" t="s">
+        <v>116</v>
+      </c>
+      <c r="D19" t="s">
+        <v>117</v>
+      </c>
+      <c r="E19" t="s">
+        <v>118</v>
+      </c>
+      <c r="F19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19"/>
+      <c r="H19" t="s">
+        <v>17</v>
+      </c>
+      <c r="I19" t="s">
+        <v>113</v>
+      </c>
+      <c r="J19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" t="s">
+        <v>119</v>
+      </c>
+      <c r="B20" t="s">
+        <v>120</v>
+      </c>
+      <c r="C20" t="s">
+        <v>121</v>
+      </c>
+      <c r="D20" t="s">
+        <v>122</v>
+      </c>
+      <c r="E20" t="s">
+        <v>123</v>
+      </c>
+      <c r="F20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20"/>
+      <c r="H20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I20" t="s">
+        <v>124</v>
+      </c>
+      <c r="J20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" t="s">
+        <v>125</v>
+      </c>
+      <c r="B21" t="s">
+        <v>126</v>
+      </c>
+      <c r="C21" t="s">
+        <v>127</v>
+      </c>
+      <c r="D21" t="s">
+        <v>128</v>
+      </c>
+      <c r="E21" t="s">
+        <v>129</v>
+      </c>
+      <c r="F21" t="s">
+        <v>66</v>
+      </c>
+      <c r="G21"/>
+      <c r="H21" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" t="s">
+        <v>130</v>
+      </c>
+      <c r="J21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" t="s">
+        <v>131</v>
+      </c>
+      <c r="B22" t="s">
+        <v>132</v>
+      </c>
+      <c r="C22" t="s">
+        <v>133</v>
+      </c>
+      <c r="D22" t="s">
+        <v>134</v>
+      </c>
+      <c r="E22" t="s">
+        <v>135</v>
+      </c>
+      <c r="F22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22"/>
+      <c r="H22" t="s">
+        <v>136</v>
+      </c>
+      <c r="I22" t="s">
+        <v>25</v>
+      </c>
+      <c r="J22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" t="s">
+        <v>137</v>
+      </c>
+      <c r="B23" t="s">
+        <v>138</v>
+      </c>
+      <c r="C23" t="s">
+        <v>139</v>
+      </c>
+      <c r="D23" t="s">
+        <v>140</v>
+      </c>
+      <c r="E23" t="s">
+        <v>141</v>
+      </c>
+      <c r="F23" t="s">
+        <v>66</v>
+      </c>
+      <c r="G23"/>
+      <c r="H23" t="s">
+        <v>136</v>
+      </c>
+      <c r="I23" t="s">
+        <v>31</v>
+      </c>
+      <c r="J23" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" t="s">
+        <v>142</v>
+      </c>
+      <c r="B24" t="s">
+        <v>143</v>
+      </c>
+      <c r="C24" t="s">
+        <v>144</v>
+      </c>
+      <c r="D24" t="s">
+        <v>145</v>
+      </c>
+      <c r="E24" t="s">
+        <v>146</v>
+      </c>
+      <c r="F24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24"/>
+      <c r="H24" t="s">
+        <v>17</v>
+      </c>
+      <c r="I24" t="s">
+        <v>25</v>
+      </c>
+      <c r="J24" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" t="s">
+        <v>147</v>
+      </c>
+      <c r="B25" t="s">
+        <v>148</v>
+      </c>
+      <c r="C25" t="s">
+        <v>149</v>
+      </c>
+      <c r="D25" t="s">
+        <v>150</v>
+      </c>
+      <c r="E25" t="s">
+        <v>151</v>
+      </c>
+      <c r="F25" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25"/>
+      <c r="H25" t="s">
+        <v>136</v>
+      </c>
+      <c r="I25" t="s">
+        <v>37</v>
+      </c>
+      <c r="J25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" t="s">
+        <v>152</v>
+      </c>
+      <c r="B26" t="s">
+        <v>153</v>
+      </c>
+      <c r="C26" t="s">
+        <v>154</v>
+      </c>
+      <c r="D26" t="s">
+        <v>155</v>
+      </c>
+      <c r="E26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F26" t="s">
+        <v>66</v>
+      </c>
+      <c r="G26"/>
+      <c r="H26" t="s">
+        <v>17</v>
+      </c>
+      <c r="I26" t="s">
+        <v>54</v>
+      </c>
+      <c r="J26" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" t="s">
+        <v>157</v>
+      </c>
+      <c r="B27" t="s">
+        <v>158</v>
+      </c>
+      <c r="C27" t="s">
+        <v>159</v>
+      </c>
+      <c r="D27" t="s">
+        <v>160</v>
+      </c>
+      <c r="E27" t="s">
+        <v>161</v>
+      </c>
+      <c r="F27" t="s">
+        <v>66</v>
+      </c>
+      <c r="G27"/>
+      <c r="H27" t="s">
+        <v>136</v>
+      </c>
+      <c r="I27" t="s">
+        <v>43</v>
+      </c>
+      <c r="J27" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" t="s">
+        <v>162</v>
+      </c>
+      <c r="B28" t="s">
+        <v>163</v>
+      </c>
+      <c r="C28" t="s">
+        <v>164</v>
+      </c>
+      <c r="D28" t="s">
+        <v>165</v>
+      </c>
+      <c r="E28" t="s">
+        <v>166</v>
+      </c>
+      <c r="F28" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28"/>
+      <c r="H28" t="s">
+        <v>17</v>
+      </c>
+      <c r="I28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" t="s">
+        <v>167</v>
+      </c>
+      <c r="B29" t="s">
+        <v>168</v>
+      </c>
+      <c r="C29" t="s">
+        <v>169</v>
+      </c>
+      <c r="D29" t="s">
+        <v>170</v>
+      </c>
+      <c r="E29" t="s">
+        <v>171</v>
+      </c>
+      <c r="F29" t="s">
+        <v>66</v>
+      </c>
+      <c r="G29"/>
+      <c r="H29" t="s">
+        <v>136</v>
+      </c>
+      <c r="I29" t="s">
+        <v>25</v>
+      </c>
+      <c r="J29" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" t="s">
+        <v>172</v>
+      </c>
+      <c r="B30" t="s">
+        <v>173</v>
+      </c>
+      <c r="C30" t="s">
+        <v>174</v>
+      </c>
+      <c r="D30" t="s">
+        <v>175</v>
+      </c>
+      <c r="E30" t="s">
+        <v>176</v>
+      </c>
+      <c r="F30" t="s">
+        <v>15</v>
+      </c>
+      <c r="G30"/>
+      <c r="H30" t="s">
+        <v>17</v>
+      </c>
+      <c r="I30" t="s">
+        <v>31</v>
+      </c>
+      <c r="J30" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" t="s">
+        <v>177</v>
+      </c>
+      <c r="B31" t="s">
+        <v>178</v>
+      </c>
+      <c r="C31" t="s">
+        <v>179</v>
+      </c>
+      <c r="D31" t="s">
+        <v>180</v>
+      </c>
+      <c r="E31" t="s">
+        <v>181</v>
+      </c>
+      <c r="F31" t="s">
+        <v>66</v>
+      </c>
+      <c r="G31"/>
+      <c r="H31" t="s">
+        <v>136</v>
+      </c>
+      <c r="I31" t="s">
+        <v>25</v>
+      </c>
+      <c r="J31" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" t="s">
+        <v>182</v>
+      </c>
+      <c r="B32" t="s">
+        <v>183</v>
+      </c>
+      <c r="C32" t="s">
+        <v>184</v>
+      </c>
+      <c r="D32" t="s">
+        <v>185</v>
+      </c>
+      <c r="E32" t="s">
+        <v>186</v>
+      </c>
+      <c r="F32" t="s">
+        <v>66</v>
+      </c>
+      <c r="G32"/>
+      <c r="H32" t="s">
+        <v>17</v>
+      </c>
+      <c r="I32" t="s">
+        <v>187</v>
+      </c>
+      <c r="J32" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" t="s">
+        <v>188</v>
+      </c>
+      <c r="B33" t="s">
+        <v>189</v>
+      </c>
+      <c r="C33" t="s">
+        <v>190</v>
+      </c>
+      <c r="D33" t="s">
+        <v>191</v>
+      </c>
+      <c r="E33" t="s">
+        <v>192</v>
+      </c>
+      <c r="F33" t="s">
+        <v>15</v>
+      </c>
+      <c r="G33"/>
+      <c r="H33" t="s">
+        <v>17</v>
+      </c>
+      <c r="I33" t="s">
+        <v>193</v>
+      </c>
+      <c r="J33" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" t="s">
+        <v>194</v>
+      </c>
+      <c r="B34" t="s">
+        <v>195</v>
+      </c>
+      <c r="C34" t="s">
+        <v>196</v>
+      </c>
+      <c r="D34" t="s">
+        <v>197</v>
+      </c>
+      <c r="E34" t="s">
+        <v>198</v>
+      </c>
+      <c r="F34" t="s">
+        <v>15</v>
+      </c>
+      <c r="G34"/>
+      <c r="H34" t="s">
+        <v>17</v>
+      </c>
+      <c r="I34" t="s">
+        <v>199</v>
+      </c>
+      <c r="J34" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" t="s">
+        <v>200</v>
+      </c>
+      <c r="B35" t="s">
+        <v>201</v>
+      </c>
+      <c r="C35" t="s">
+        <v>202</v>
+      </c>
+      <c r="D35" t="s">
+        <v>203</v>
+      </c>
+      <c r="E35" t="s">
+        <v>204</v>
+      </c>
+      <c r="F35" t="s">
+        <v>66</v>
+      </c>
+      <c r="G35"/>
+      <c r="H35" t="s">
+        <v>17</v>
+      </c>
+      <c r="I35" t="s">
+        <v>205</v>
+      </c>
+      <c r="J35" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" t="s">
+        <v>206</v>
+      </c>
+      <c r="B36" t="s">
+        <v>207</v>
+      </c>
+      <c r="C36" t="s">
+        <v>208</v>
+      </c>
+      <c r="D36" t="s">
+        <v>209</v>
+      </c>
+      <c r="E36" t="s">
+        <v>210</v>
+      </c>
+      <c r="F36" t="s">
+        <v>66</v>
+      </c>
+      <c r="G36"/>
+      <c r="H36" t="s">
+        <v>17</v>
+      </c>
+      <c r="I36" t="s">
+        <v>211</v>
+      </c>
+      <c r="J36" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" t="s">
+        <v>212</v>
+      </c>
+      <c r="B37" t="s">
+        <v>213</v>
+      </c>
+      <c r="C37" t="s">
+        <v>214</v>
+      </c>
+      <c r="D37" t="s">
+        <v>215</v>
+      </c>
+      <c r="E37" t="s">
+        <v>216</v>
+      </c>
+      <c r="F37" t="s">
+        <v>15</v>
+      </c>
+      <c r="G37"/>
+      <c r="H37" t="s">
+        <v>17</v>
+      </c>
+      <c r="I37" t="s">
+        <v>217</v>
+      </c>
+      <c r="J37" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" t="s">
+        <v>218</v>
+      </c>
+      <c r="B38" t="s">
+        <v>219</v>
+      </c>
+      <c r="C38" t="s">
+        <v>220</v>
+      </c>
+      <c r="D38" t="s">
+        <v>221</v>
+      </c>
+      <c r="E38" t="s">
+        <v>222</v>
+      </c>
+      <c r="F38" t="s">
+        <v>15</v>
+      </c>
+      <c r="G38" t="s">
+        <v>16</v>
+      </c>
+      <c r="H38" t="s">
+        <v>17</v>
+      </c>
+      <c r="I38" t="s">
+        <v>223</v>
+      </c>
+      <c r="J38" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" t="s">
+        <v>224</v>
+      </c>
+      <c r="B39" t="s">
+        <v>225</v>
+      </c>
+      <c r="C39" t="s">
+        <v>226</v>
+      </c>
+      <c r="D39" t="s">
+        <v>227</v>
+      </c>
+      <c r="E39" t="s">
+        <v>228</v>
+      </c>
+      <c r="F39" t="s">
+        <v>15</v>
+      </c>
+      <c r="G39"/>
+      <c r="H39" t="s">
+        <v>136</v>
+      </c>
+      <c r="I39" t="s">
+        <v>25</v>
+      </c>
+      <c r="J39" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" t="s">
+        <v>229</v>
+      </c>
+      <c r="B40" t="s">
+        <v>230</v>
+      </c>
+      <c r="C40" t="s">
+        <v>231</v>
+      </c>
+      <c r="D40" t="s">
+        <v>232</v>
+      </c>
+      <c r="E40" t="s">
+        <v>233</v>
+      </c>
+      <c r="F40" t="s">
+        <v>66</v>
+      </c>
+      <c r="G40"/>
+      <c r="H40" t="s">
+        <v>136</v>
+      </c>
+      <c r="I40" t="s">
+        <v>31</v>
+      </c>
+      <c r="J40" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" t="s">
+        <v>234</v>
+      </c>
+      <c r="B41" t="s">
+        <v>235</v>
+      </c>
+      <c r="C41" t="s">
+        <v>236</v>
+      </c>
+      <c r="D41" t="s">
+        <v>237</v>
+      </c>
+      <c r="E41" t="s">
+        <v>238</v>
+      </c>
+      <c r="F41" t="s">
+        <v>15</v>
+      </c>
+      <c r="G41"/>
+      <c r="H41" t="s">
+        <v>17</v>
+      </c>
+      <c r="I41" t="s">
+        <v>37</v>
+      </c>
+      <c r="J41" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" t="s">
+        <v>239</v>
+      </c>
+      <c r="B42" t="s">
+        <v>240</v>
+      </c>
+      <c r="C42" t="s">
+        <v>241</v>
+      </c>
+      <c r="D42" t="s">
+        <v>242</v>
+      </c>
+      <c r="E42" t="s">
+        <v>243</v>
+      </c>
+      <c r="F42" t="s">
+        <v>15</v>
+      </c>
+      <c r="G42"/>
+      <c r="H42" t="s">
+        <v>136</v>
+      </c>
+      <c r="I42" t="s">
+        <v>43</v>
+      </c>
+      <c r="J42" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" t="s">
+        <v>244</v>
+      </c>
+      <c r="B43" t="s">
+        <v>245</v>
+      </c>
+      <c r="C43" t="s">
+        <v>246</v>
+      </c>
+      <c r="D43" t="s">
+        <v>247</v>
+      </c>
+      <c r="E43" t="s">
+        <v>248</v>
+      </c>
+      <c r="F43" t="s">
+        <v>66</v>
+      </c>
+      <c r="G43"/>
+      <c r="H43" t="s">
+        <v>17</v>
+      </c>
+      <c r="I43" t="s">
+        <v>54</v>
+      </c>
+      <c r="J43" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" t="s">
+        <v>249</v>
+      </c>
+      <c r="B44" t="s">
+        <v>250</v>
+      </c>
+      <c r="C44" t="s">
+        <v>251</v>
+      </c>
+      <c r="D44" t="s">
+        <v>252</v>
+      </c>
+      <c r="E44" t="s">
+        <v>253</v>
+      </c>
+      <c r="F44" t="s">
+        <v>15</v>
+      </c>
+      <c r="G44"/>
+      <c r="H44" t="s">
+        <v>136</v>
+      </c>
+      <c r="I44" t="s">
+        <v>18</v>
+      </c>
+      <c r="J44" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" t="s">
+        <v>254</v>
+      </c>
+      <c r="B45" t="s">
+        <v>255</v>
+      </c>
+      <c r="C45" t="s">
+        <v>256</v>
+      </c>
+      <c r="D45" t="s">
+        <v>257</v>
+      </c>
+      <c r="E45" t="s">
+        <v>258</v>
+      </c>
+      <c r="F45" t="s">
+        <v>15</v>
+      </c>
+      <c r="G45"/>
+      <c r="H45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I45" t="s">
+        <v>25</v>
+      </c>
+      <c r="J45" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" t="s">
+        <v>259</v>
+      </c>
+      <c r="B46" t="s">
+        <v>260</v>
+      </c>
+      <c r="C46" t="s">
+        <v>261</v>
+      </c>
+      <c r="D46" t="s">
+        <v>262</v>
+      </c>
+      <c r="E46" t="s">
+        <v>263</v>
+      </c>
+      <c r="F46" t="s">
+        <v>66</v>
+      </c>
+      <c r="G46"/>
+      <c r="H46" t="s">
+        <v>136</v>
+      </c>
+      <c r="I46" t="s">
+        <v>31</v>
+      </c>
+      <c r="J46" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" t="s">
+        <v>264</v>
+      </c>
+      <c r="B47" t="s">
+        <v>265</v>
+      </c>
+      <c r="C47" t="s">
+        <v>266</v>
+      </c>
+      <c r="D47" t="s">
+        <v>267</v>
+      </c>
+      <c r="E47" t="s">
+        <v>268</v>
+      </c>
+      <c r="F47" t="s">
+        <v>15</v>
+      </c>
+      <c r="G47"/>
+      <c r="H47" t="s">
+        <v>17</v>
+      </c>
+      <c r="I47" t="s">
+        <v>37</v>
+      </c>
+      <c r="J47" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" t="s">
+        <v>269</v>
+      </c>
+      <c r="B48" t="s">
+        <v>270</v>
+      </c>
+      <c r="C48" t="s">
+        <v>271</v>
+      </c>
+      <c r="D48" t="s">
+        <v>272</v>
+      </c>
+      <c r="E48" t="s">
+        <v>273</v>
+      </c>
+      <c r="F48" t="s">
+        <v>66</v>
+      </c>
+      <c r="G48"/>
+      <c r="H48" t="s">
+        <v>136</v>
+      </c>
+      <c r="I48" t="s">
+        <v>68</v>
+      </c>
+      <c r="J48" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" t="s">
+        <v>274</v>
+      </c>
+      <c r="B49" t="s">
+        <v>275</v>
+      </c>
+      <c r="C49" t="s">
+        <v>276</v>
+      </c>
+      <c r="D49" t="s">
+        <v>277</v>
+      </c>
+      <c r="E49" t="s">
+        <v>278</v>
+      </c>
+      <c r="F49" t="s">
+        <v>15</v>
+      </c>
+      <c r="G49"/>
+      <c r="H49" t="s">
+        <v>17</v>
+      </c>
+      <c r="I49" t="s">
+        <v>74</v>
+      </c>
+      <c r="J49" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" t="s">
+        <v>279</v>
+      </c>
+      <c r="B50" t="s">
+        <v>280</v>
+      </c>
+      <c r="C50" t="s">
+        <v>281</v>
+      </c>
+      <c r="D50" t="s">
+        <v>282</v>
+      </c>
+      <c r="E50" t="s">
+        <v>283</v>
+      </c>
+      <c r="F50" t="s">
+        <v>66</v>
+      </c>
+      <c r="G50"/>
+      <c r="H50" t="s">
+        <v>136</v>
+      </c>
+      <c r="I50" t="s">
+        <v>130</v>
+      </c>
+      <c r="J50" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" t="s">
+        <v>284</v>
+      </c>
+      <c r="B51" t="s">
+        <v>285</v>
+      </c>
+      <c r="C51" t="s">
+        <v>286</v>
+      </c>
+      <c r="D51" t="s">
+        <v>287</v>
+      </c>
+      <c r="E51" t="s">
+        <v>288</v>
+      </c>
+      <c r="F51" t="s">
+        <v>15</v>
+      </c>
+      <c r="G51"/>
+      <c r="H51" t="s">
+        <v>17</v>
+      </c>
+      <c r="I51" t="s">
+        <v>113</v>
+      </c>
+      <c r="J51" t="s">
         <v>19</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells>
-    <mergeCell ref="A1:J1"/>
-  </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/sample_imports/06_GiangVien_Mau.xlsx
+++ b/sample_imports/06_GiangVien_Mau.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="284">
   <si>
     <t>MaGV</t>
   </si>
@@ -47,7 +47,7 @@
     <t>TrangThai</t>
   </si>
   <si>
-    <t>GV001</t>
+    <t>GV00000001</t>
   </si>
   <si>
     <t>PGS.TS. Nguyễn Văn Hùng</t>
@@ -77,7 +77,7 @@
     <t>Đang công tác</t>
   </si>
   <si>
-    <t>GV002</t>
+    <t>GV00000002</t>
   </si>
   <si>
     <t>TS. Trần Anh Dũng</t>
@@ -95,7 +95,7 @@
     <t>CNPM</t>
   </si>
   <si>
-    <t>GV003</t>
+    <t>GV00000003</t>
   </si>
   <si>
     <t>TS. Phạm Minh Tuấn</t>
@@ -113,7 +113,7 @@
     <t>HTTT</t>
   </si>
   <si>
-    <t>GV004</t>
+    <t>GV00000004</t>
   </si>
   <si>
     <t>TS. Trịnh Văn Thành</t>
@@ -131,7 +131,7 @@
     <t>ATTT</t>
   </si>
   <si>
-    <t>GV005</t>
+    <t>GV00000005</t>
   </si>
   <si>
     <t>TS. Lê Hải Đăng</t>
@@ -149,7 +149,7 @@
     <t>MMT</t>
   </si>
   <si>
-    <t>GV006</t>
+    <t>GV00000006</t>
   </si>
   <si>
     <t>PGS.TS. Võ Quốc Phong</t>
@@ -164,7 +164,7 @@
     <t>1976-09-30</t>
   </si>
   <si>
-    <t>GV007</t>
+    <t>GV00000007</t>
   </si>
   <si>
     <t>TS. Đỗ Anh Minh</t>
@@ -182,7 +182,7 @@
     <t>KHDL</t>
   </si>
   <si>
-    <t>GV008</t>
+    <t>GV00000008</t>
   </si>
   <si>
     <t>PGS.TS. Trần Đình Nam</t>
@@ -200,7 +200,7 @@
     <t>QTKD_DN</t>
   </si>
   <si>
-    <t>GV009</t>
+    <t>GV00000009</t>
   </si>
   <si>
     <t>GS.TS. Lê Thị Mai</t>
@@ -224,7 +224,7 @@
     <t>CBTP</t>
   </si>
   <si>
-    <t>GV010</t>
+    <t>GV00000010</t>
   </si>
   <si>
     <t>PGS.TS. Vũ Trọng Hưng</t>
@@ -242,7 +242,7 @@
     <t>KTD</t>
   </si>
   <si>
-    <t>GV011</t>
+    <t>GV00000011</t>
   </si>
   <si>
     <t>TS. Bùi Thu Hà</t>
@@ -257,7 +257,7 @@
     <t>1983-10-10</t>
   </si>
   <si>
-    <t>GV012</t>
+    <t>GV00000012</t>
   </si>
   <si>
     <t>TS. Nguyễn Văn An</t>
@@ -275,7 +275,7 @@
     <t>MKT</t>
   </si>
   <si>
-    <t>GV013</t>
+    <t>GV00000013</t>
   </si>
   <si>
     <t>PGS.TS. Đỗ Hoài Nam</t>
@@ -290,7 +290,7 @@
     <t>1977-03-08</t>
   </si>
   <si>
-    <t>GV014</t>
+    <t>GV00000014</t>
   </si>
   <si>
     <t>TS. Trương Tuyết Mai</t>
@@ -308,7 +308,7 @@
     <t>DBTP</t>
   </si>
   <si>
-    <t>GV015</t>
+    <t>GV00000015</t>
   </si>
   <si>
     <t>TS. Vũ Anh Quân</t>
@@ -323,7 +323,7 @@
     <t>1982-04-03</t>
   </si>
   <si>
-    <t>GV016</t>
+    <t>GV00000016</t>
   </si>
   <si>
     <t>TS. Hồ Vĩnh Thắng</t>
@@ -341,7 +341,7 @@
     <t>DT</t>
   </si>
   <si>
-    <t>GV017</t>
+    <t>GV00000017</t>
   </si>
   <si>
     <t>PGS.TS. Đặng Quốc Thịnh</t>
@@ -359,7 +359,7 @@
     <t>CTM</t>
   </si>
   <si>
-    <t>GV018</t>
+    <t>GV00000018</t>
   </si>
   <si>
     <t>TS. Phan Trọng Nghĩa</t>
@@ -374,7 +374,7 @@
     <t>1983-02-11</t>
   </si>
   <si>
-    <t>GV019</t>
+    <t>GV00000019</t>
   </si>
   <si>
     <t>TS. Chu Văn Quân</t>
@@ -392,7 +392,7 @@
     <t>CDT</t>
   </si>
   <si>
-    <t>GV020</t>
+    <t>GV00000020</t>
   </si>
   <si>
     <t>TS. Phạm Thị Bích Loan</t>
@@ -410,7 +410,7 @@
     <t>TA_CN</t>
   </si>
   <si>
-    <t>GV021</t>
+    <t>GV00000021</t>
   </si>
   <si>
     <t>ThS. Đặng Hải Giang</t>
@@ -428,7 +428,7 @@
     <t>Thạc sĩ</t>
   </si>
   <si>
-    <t>GV022</t>
+    <t>GV00000022</t>
   </si>
   <si>
     <t>ThS. Trần Thị Bích</t>
@@ -443,7 +443,7 @@
     <t>1989-09-02</t>
   </si>
   <si>
-    <t>GV023</t>
+    <t>GV00000023</t>
   </si>
   <si>
     <t>TS. Lê Hoàng Cường</t>
@@ -458,7 +458,7 @@
     <t>1984-12-18</t>
   </si>
   <si>
-    <t>GV024</t>
+    <t>GV00000024</t>
   </si>
   <si>
     <t>ThS. Ngô Đức Hải</t>
@@ -473,7 +473,7 @@
     <t>1990-07-07</t>
   </si>
   <si>
-    <t>GV025</t>
+    <t>GV00000025</t>
   </si>
   <si>
     <t>TS. Dương Thúy Hằng</t>
@@ -488,7 +488,7 @@
     <t>1983-04-26</t>
   </si>
   <si>
-    <t>GV026</t>
+    <t>GV00000026</t>
   </si>
   <si>
     <t>ThS. Lý Thanh Lan</t>
@@ -503,7 +503,7 @@
     <t>1991-02-14</t>
   </si>
   <si>
-    <t>GV027</t>
+    <t>GV00000027</t>
   </si>
   <si>
     <t>TS. Trịnh Văn Khang</t>
@@ -518,7 +518,7 @@
     <t>1982-08-09</t>
   </si>
   <si>
-    <t>GV028</t>
+    <t>GV00000028</t>
   </si>
   <si>
     <t>ThS. Mai Tuyết Nga</t>
@@ -533,7 +533,7 @@
     <t>1987-11-21</t>
   </si>
   <si>
-    <t>GV029</t>
+    <t>GV00000029</t>
   </si>
   <si>
     <t>TS. Võ Đình Phúc</t>
@@ -548,7 +548,7 @@
     <t>1980-03-31</t>
   </si>
   <si>
-    <t>GV030</t>
+    <t>GV00000030</t>
   </si>
   <si>
     <t>ThS. Hoàng Thị Em</t>
@@ -563,7 +563,7 @@
     <t>1992-01-19</t>
   </si>
   <si>
-    <t>GV031</t>
+    <t>GV00000031</t>
   </si>
   <si>
     <t>TS. Đinh Hoàng Xuân</t>
@@ -581,7 +581,7 @@
     <t>KT</t>
   </si>
   <si>
-    <t>GV032</t>
+    <t>GV00000032</t>
   </si>
   <si>
     <t>TS. Cao Thái Vinh</t>
@@ -599,7 +599,7 @@
     <t>TC</t>
   </si>
   <si>
-    <t>GV033</t>
+    <t>GV00000033</t>
   </si>
   <si>
     <t>TS. Phan Văn Phúc</t>
@@ -617,7 +617,7 @@
     <t>LKTE</t>
   </si>
   <si>
-    <t>GV034</t>
+    <t>GV00000034</t>
   </si>
   <si>
     <t>TS. Hoàng Yến Linh</t>
@@ -635,7 +635,7 @@
     <t>QTDL</t>
   </si>
   <si>
-    <t>GV035</t>
+    <t>GV00000035</t>
   </si>
   <si>
     <t>TS. Bùi Mai Hoa</t>
@@ -653,7 +653,7 @@
     <t>KHMT_MT</t>
   </si>
   <si>
-    <t>GV036</t>
+    <t>GV00000036</t>
   </si>
   <si>
     <t>TS. Võ Duy Hùng</t>
@@ -671,7 +671,7 @@
     <t>TMDT_SO</t>
   </si>
   <si>
-    <t>GV037</t>
+    <t>GV00000037</t>
   </si>
   <si>
     <t>PGS.TS. Mai Thế Vinh</t>
@@ -689,7 +689,7 @@
     <t>LOG_CCU</t>
   </si>
   <si>
-    <t>GV038</t>
+    <t>GV00000038</t>
   </si>
   <si>
     <t>ThS. Nguyễn Hoàng Anh</t>
@@ -704,7 +704,7 @@
     <t>1989-08-18</t>
   </si>
   <si>
-    <t>GV039</t>
+    <t>GV00000039</t>
   </si>
   <si>
     <t>ThS. Lê Phương Thảo</t>
@@ -719,7 +719,7 @@
     <t>1990-12-03</t>
   </si>
   <si>
-    <t>GV040</t>
+    <t>GV00000040</t>
   </si>
   <si>
     <t>TS. Vũ Đình Khôi</t>
@@ -734,7 +734,7 @@
     <t>1984-04-17</t>
   </si>
   <si>
-    <t>GV041</t>
+    <t>GV00000041</t>
   </si>
   <si>
     <t>ThS. Huỳnh Quốc Bảo</t>
@@ -749,7 +749,7 @@
     <t>1991-03-25</t>
   </si>
   <si>
-    <t>GV042</t>
+    <t>GV00000042</t>
   </si>
   <si>
     <t>TS. Tôn Nữ Quỳnh Như</t>
@@ -764,7 +764,7 @@
     <t>1987-10-30</t>
   </si>
   <si>
-    <t>GV043</t>
+    <t>GV00000043</t>
   </si>
   <si>
     <t>ThS. Cù Huy Sơn</t>
@@ -779,7 +779,7 @@
     <t>1988-06-19</t>
   </si>
   <si>
-    <t>GV044</t>
+    <t>GV00000044</t>
   </si>
   <si>
     <t>TS. Thạch Văn Tài</t>
@@ -794,7 +794,7 @@
     <t>1983-01-08</t>
   </si>
   <si>
-    <t>GV045</t>
+    <t>GV00000045</t>
   </si>
   <si>
     <t>ThS. Uông Thị Uyên</t>
@@ -809,7 +809,7 @@
     <t>1992-09-14</t>
   </si>
   <si>
-    <t>GV046</t>
+    <t>GV00000046</t>
   </si>
   <si>
     <t>TS. Phí Văn Việt</t>
@@ -824,7 +824,7 @@
     <t>1985-05-22</t>
   </si>
   <si>
-    <t>GV047</t>
+    <t>GV00000047</t>
   </si>
   <si>
     <t>ThS. Mạc Thị Xuyến</t>
@@ -839,7 +839,7 @@
     <t>1990-08-04</t>
   </si>
   <si>
-    <t>GV048</t>
+    <t>GV00000048</t>
   </si>
   <si>
     <t>TS. La Quốc Ý</t>
@@ -854,7 +854,7 @@
     <t>1982-12-16</t>
   </si>
   <si>
-    <t>GV049</t>
+    <t>GV00000049</t>
   </si>
   <si>
     <t>ThS. Sầm Ngọc Anh</t>
@@ -867,21 +867,6 @@
   </si>
   <si>
     <t>1993-04-11</t>
-  </si>
-  <si>
-    <t>GV050</t>
-  </si>
-  <si>
-    <t>TS. Nông Văn Bắc</t>
-  </si>
-  <si>
-    <t>bacnv@huit.edu.vn</t>
-  </si>
-  <si>
-    <t>0903123050</t>
-  </si>
-  <si>
-    <t>1981-07-29</t>
   </si>
 </sst>
 </file>
@@ -1221,10 +1206,10 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="6.998" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="12.854" bestFit="true" customWidth="true" style="0"/>
     <col min="2" max="2" width="28.136" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="23.423" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="13.997" bestFit="true" customWidth="true" style="0"/>
@@ -2751,36 +2736,6 @@
         <v>130</v>
       </c>
       <c r="J50" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10">
-      <c r="A51" t="s">
-        <v>284</v>
-      </c>
-      <c r="B51" t="s">
-        <v>285</v>
-      </c>
-      <c r="C51" t="s">
-        <v>286</v>
-      </c>
-      <c r="D51" t="s">
-        <v>287</v>
-      </c>
-      <c r="E51" t="s">
-        <v>288</v>
-      </c>
-      <c r="F51" t="s">
-        <v>15</v>
-      </c>
-      <c r="G51"/>
-      <c r="H51" t="s">
-        <v>17</v>
-      </c>
-      <c r="I51" t="s">
-        <v>113</v>
-      </c>
-      <c r="J51" t="s">
         <v>19</v>
       </c>
     </row>
